--- a/src/nist_gas_srm/core/data/template.xlsx
+++ b/src/nist_gas_srm/core/data/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wpk/gits/nist-gas-srm-certificate/nist-gas-srm/tmp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wpk/gits/nist-gas-srm-certificate/nist-gas-srm/src/nist_gas_srm/core/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6269208-533F-9341-8BC3-3FFFDBB47C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ECE6C9-74B2-3F42-98C1-1BE1B85AC2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27980" windowHeight="27720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2000" yWindow="660" windowWidth="27980" windowHeight="21680" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ratio Data" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="324">
   <si>
     <t>SampleID</t>
   </si>
@@ -873,9 +873,6 @@
     <t>Residual</t>
   </si>
   <si>
-    <t>GENLINE - Linear (y=b0+b1*x)</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -909,27 +906,6 @@
     <t>X Variable 1</t>
   </si>
   <si>
-    <t>rms residual error</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>X-Solution</t>
-  </si>
-  <si>
-    <t>Y-Solution</t>
-  </si>
-  <si>
-    <t>uTest</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
     <t>RESIDUAL OUTPUT</t>
   </si>
   <si>
@@ -940,18 +916,6 @@
   </si>
   <si>
     <t>Residuals</t>
-  </si>
-  <si>
-    <t>Xin</t>
-  </si>
-  <si>
-    <t>uXin</t>
-  </si>
-  <si>
-    <t>Yeval</t>
-  </si>
-  <si>
-    <t>uYeval</t>
   </si>
   <si>
     <t>Step 6.</t>
@@ -1490,6 +1454,9 @@
   </si>
   <si>
     <t>l</t>
+  </si>
+  <si>
+    <t>,</t>
   </si>
 </sst>
 </file>
@@ -2609,7 +2576,7 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="500">
+  <cellXfs count="499">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3675,7 +3642,6 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="46" xfId="12" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -5509,7 +5475,7 @@
       <c r="K13" s="469"/>
       <c r="L13" s="470">
         <f>'Std Analysis'!L5</f>
-        <v>5.1393653353487503</v>
+        <v>0</v>
       </c>
       <c r="M13" s="469"/>
       <c r="N13" s="471"/>
@@ -36204,7 +36170,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X79"/>
+  <dimension ref="A1:X70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="11" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="10.19921875" customWidth="1"/>
@@ -36378,14 +36344,8 @@
       <c r="J5" s="251" t="s">
         <v>188</v>
       </c>
-      <c r="L5" s="252">
-        <f>V36</f>
-        <v>5.1393653353487503</v>
-      </c>
-      <c r="M5" s="253">
-        <f>W36</f>
-        <v>5.4762915734571597E-3</v>
-      </c>
+      <c r="L5" s="252"/>
+      <c r="M5" s="253"/>
       <c r="N5" s="7" t="s">
         <v>189</v>
       </c>
@@ -36515,12 +36475,8 @@
       <c r="J8" s="258" t="s">
         <v>201</v>
       </c>
-      <c r="L8" s="259">
-        <v>5.1410537607056304</v>
-      </c>
-      <c r="M8" s="260">
-        <v>3.2141640636213298E-3</v>
-      </c>
+      <c r="L8" s="259"/>
+      <c r="M8" s="260"/>
       <c r="N8" s="7" t="s">
         <v>202</v>
       </c>
@@ -36548,12 +36504,8 @@
       <c r="E9" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="L9" s="261">
-        <v>5.0084643206758299</v>
-      </c>
-      <c r="M9" s="262">
-        <v>1.20501206497283E-2</v>
-      </c>
+      <c r="L9" s="261"/>
+      <c r="M9" s="262"/>
       <c r="N9" s="7" t="s">
         <v>204</v>
       </c>
@@ -36581,12 +36533,8 @@
       <c r="A10" t="s">
         <v>205</v>
       </c>
-      <c r="L10" s="263">
-        <v>0.132589440029796</v>
-      </c>
-      <c r="M10" s="264">
-        <v>1.2703591313119499E-2</v>
-      </c>
+      <c r="L10" s="263"/>
+      <c r="M10" s="264"/>
       <c r="N10" s="7" t="s">
         <v>206</v>
       </c>
@@ -36770,9 +36718,7 @@
         <v>225</v>
       </c>
       <c r="S22" s="275"/>
-      <c r="T22" s="224" t="s">
-        <v>226</v>
-      </c>
+      <c r="T22" s="224"/>
       <c r="U22" s="224"/>
       <c r="V22" s="224"/>
       <c r="W22" s="224"/>
@@ -36780,7 +36726,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A23" s="191" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B23" s="191">
         <f>SUM(B21:B22)</f>
@@ -36796,7 +36742,7 @@
       <c r="S23" s="276"/>
       <c r="T23" s="277"/>
       <c r="U23" s="277" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="V23" s="277" t="s">
         <v>120</v>
@@ -36807,59 +36753,49 @@
     <row r="24" spans="1:24" x14ac:dyDescent="0.15">
       <c r="S24" s="276"/>
       <c r="T24" s="277" t="s">
-        <v>82</v>
-      </c>
-      <c r="U24" s="277">
-        <v>0.11912533273877</v>
-      </c>
-      <c r="V24" s="277">
-        <v>1.97568371496279E-2</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="U24" s="277"/>
+      <c r="V24" s="277"/>
       <c r="W24" s="277"/>
       <c r="X24" s="250"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>214</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="S25" s="276"/>
-      <c r="T25" s="277" t="s">
-        <v>85</v>
-      </c>
-      <c r="U25" s="277">
-        <v>5.02024000260998</v>
-      </c>
-      <c r="V25" s="277">
-        <v>1.9046724159365501E-2</v>
-      </c>
+      <c r="T25" s="277"/>
+      <c r="U25" s="277"/>
+      <c r="V25" s="277"/>
       <c r="W25" s="277"/>
       <c r="X25" s="250"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H26">
         <f>F26</f>
@@ -36870,19 +36806,15 @@
         <v>0</v>
       </c>
       <c r="S26" s="276"/>
-      <c r="T26" s="277" t="s">
-        <v>71</v>
-      </c>
+      <c r="T26" s="277"/>
       <c r="U26" s="277"/>
-      <c r="V26" s="277">
-        <v>-3.6156027298117702E-4</v>
-      </c>
+      <c r="V26" s="277"/>
       <c r="W26" s="277"/>
       <c r="X26" s="250"/>
     </row>
     <row r="27" spans="1:24" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="191" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B27" s="191"/>
       <c r="C27" s="191"/>
@@ -36899,13 +36831,9 @@
         <v>0</v>
       </c>
       <c r="S27" s="276"/>
-      <c r="T27" s="277" t="s">
-        <v>238</v>
-      </c>
+      <c r="T27" s="277"/>
       <c r="U27" s="277"/>
-      <c r="V27" s="277">
-        <v>1.4688555439562001</v>
-      </c>
+      <c r="V27" s="277"/>
       <c r="W27" s="277"/>
       <c r="X27" s="250"/>
     </row>
@@ -36919,105 +36847,55 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.15">
       <c r="S29" s="276"/>
-      <c r="T29" s="277" t="s">
-        <v>239</v>
-      </c>
-      <c r="U29" s="277" t="s">
-        <v>240</v>
-      </c>
-      <c r="V29" s="278" t="s">
-        <v>241</v>
-      </c>
-      <c r="W29" s="277" t="s">
-        <v>242</v>
-      </c>
-      <c r="X29" s="250" t="s">
-        <v>243</v>
-      </c>
+      <c r="T29" s="277"/>
+      <c r="U29" s="277"/>
+      <c r="V29" s="278"/>
+      <c r="W29" s="277"/>
+      <c r="X29" s="250"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.15">
       <c r="S30" s="279"/>
-      <c r="T30" s="156">
-        <v>0.776234064991009</v>
-      </c>
-      <c r="U30" s="156">
-        <v>4.0068999999999999</v>
-      </c>
-      <c r="V30" s="156">
-        <v>0.77612627472496099</v>
-      </c>
-      <c r="W30" s="156">
-        <v>4.0154655015724297</v>
-      </c>
-      <c r="X30" s="250" t="s">
-        <v>244</v>
-      </c>
+      <c r="T30" s="156"/>
+      <c r="U30" s="156"/>
+      <c r="V30" s="156"/>
+      <c r="W30" s="156"/>
+      <c r="X30" s="250"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="S31" s="279"/>
-      <c r="T31" s="156">
-        <v>0.96322449960561896</v>
-      </c>
-      <c r="U31" s="156">
-        <v>4.9720000000000004</v>
-      </c>
-      <c r="V31" s="156">
-        <v>0.96355490923115295</v>
-      </c>
-      <c r="W31" s="156">
-        <v>4.9564022393490701</v>
-      </c>
-      <c r="X31" s="250" t="s">
-        <v>244</v>
-      </c>
+      <c r="T31" s="156"/>
+      <c r="U31" s="156"/>
+      <c r="V31" s="156"/>
+      <c r="W31" s="156"/>
+      <c r="X31" s="250"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.15">
       <c r="S32" s="279"/>
-      <c r="T32" s="156">
-        <v>1.1783329936339799</v>
-      </c>
-      <c r="U32" s="156">
-        <v>6.0359999999999996</v>
-      </c>
-      <c r="V32" s="156">
-        <v>1.17834561530417</v>
-      </c>
-      <c r="W32" s="156">
-        <v>6.0347031261822304</v>
-      </c>
-      <c r="X32" s="250" t="s">
-        <v>244</v>
-      </c>
+      <c r="T32" s="156"/>
+      <c r="U32" s="156"/>
+      <c r="V32" s="156"/>
+      <c r="W32" s="156"/>
+      <c r="X32" s="250"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="S33" s="279"/>
-      <c r="T33" s="156">
-        <v>1.7726021202370901</v>
-      </c>
-      <c r="U33" s="156">
-        <v>9.0069999999999997</v>
-      </c>
-      <c r="V33" s="156">
-        <v>1.7725584060181201</v>
-      </c>
-      <c r="W33" s="156">
-        <v>9.0177939443628006</v>
-      </c>
-      <c r="X33" s="250" t="s">
-        <v>244</v>
-      </c>
+      <c r="T33" s="156"/>
+      <c r="U33" s="156"/>
+      <c r="V33" s="156"/>
+      <c r="W33" s="156"/>
+      <c r="X33" s="250"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.15">
       <c r="J34" t="e">
@@ -37033,94 +36911,54 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.15">
       <c r="S35" s="279"/>
-      <c r="T35" s="156" t="s">
-        <v>249</v>
-      </c>
-      <c r="U35" s="156" t="s">
-        <v>250</v>
-      </c>
-      <c r="V35" s="156" t="s">
-        <v>251</v>
-      </c>
-      <c r="W35" s="156" t="s">
-        <v>252</v>
-      </c>
+      <c r="T35" s="156"/>
+      <c r="U35" s="156"/>
+      <c r="V35" s="156"/>
+      <c r="W35" s="156"/>
       <c r="X35" s="250"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.15">
       <c r="S36" s="280" t="str">
         <f>IF(T36=1,"LS# 1",IF(T36="Xin","",IF(ISBLANK(T36),"",IF(T36='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T36='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T36='Past LS'!$O$25,CONCATENATE('Past LS'!$O$23,," ",'Past LS'!$O$24),"ERROR"))))))</f>
-        <v>LS# 1</v>
-      </c>
-      <c r="T36" s="156">
-        <v>1</v>
-      </c>
-      <c r="U36" s="156">
-        <v>0</v>
-      </c>
-      <c r="V36" s="156">
-        <v>5.1393653353487503</v>
-      </c>
-      <c r="W36" s="156">
-        <v>5.4762915734571597E-3</v>
-      </c>
+        <v/>
+      </c>
+      <c r="T36" s="156"/>
+      <c r="U36" s="156"/>
+      <c r="V36" s="156"/>
+      <c r="W36" s="156"/>
       <c r="X36" s="250"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="S37" s="280" t="e">
+      <c r="S37" s="280" t="str">
         <f>IF(T37=1,"LS# 1",IF(T37="Xin","",IF(ISBLANK(T37),"",IF(T37='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T37='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T37='Past LS'!$O$25,CONCATENATE('Past LS'!$O$23,," ",'Past LS'!$O$24),"ERROR"))))))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T37" s="156">
-        <v>1.00099636396931</v>
-      </c>
-      <c r="U37" s="156">
-        <v>1.2508204255391701E-4</v>
-      </c>
-      <c r="V37" s="156">
-        <v>5.1443673216046504</v>
-      </c>
-      <c r="W37" s="156">
-        <v>5.51242837067037E-3</v>
-      </c>
+        <v/>
+      </c>
+      <c r="T37" s="156"/>
+      <c r="U37" s="156"/>
+      <c r="V37" s="156"/>
+      <c r="W37" s="156"/>
       <c r="X37" s="250"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="S38" s="280" t="e">
+      <c r="S38" s="280" t="str">
         <f>IF(T38=1,"LS# 1",IF(T38="Xin","",IF(ISBLANK(T38),"",IF(T38='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T38='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T38='Past LS'!$O$25,CONCATENATE('Past LS'!$O$23,," ",'Past LS'!$O$24),"ERROR"))))))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T38" s="156">
-        <v>0.99695906603513196</v>
-      </c>
-      <c r="U38" s="156">
-        <v>1.4865740025877901E-4</v>
-      </c>
-      <c r="V38" s="156">
-        <v>5.1240991170130297</v>
-      </c>
-      <c r="W38" s="156">
-        <v>5.5265429817113899E-3</v>
-      </c>
+        <v/>
+      </c>
+      <c r="T38" s="156"/>
+      <c r="U38" s="156"/>
+      <c r="V38" s="156"/>
+      <c r="W38" s="156"/>
       <c r="X38" s="250"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="S39" s="280" t="e">
+      <c r="S39" s="280" t="str">
         <f>IF(T39=1,"LS# 1",IF(T39="Xin","",IF(ISBLANK(T39),"",IF(T39='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T39='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T39='Past LS'!$O$25,CONCATENATE('Past LS'!$O$23,," ",'Past LS'!$O$24),"ERROR"))))))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T39" s="156">
-        <v>1.0021489855652499</v>
-      </c>
-      <c r="U39" s="156">
-        <v>1.2365776940853E-4</v>
-      </c>
-      <c r="V39" s="156">
-        <v>5.15015375864846</v>
-      </c>
-      <c r="W39" s="156">
-        <v>5.5119923382955698E-3</v>
-      </c>
+        <v/>
+      </c>
+      <c r="T39" s="156"/>
+      <c r="U39" s="156"/>
+      <c r="V39" s="156"/>
+      <c r="W39" s="156"/>
       <c r="X39" s="250"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.15">
@@ -37398,7 +37236,7 @@
       <c r="W64" s="156"/>
       <c r="X64" s="250"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="65" spans="19:24" x14ac:dyDescent="0.15">
       <c r="S65" s="280" t="str">
         <f>IF(T65=1,"LS# 1",IF(T65="Xin","",IF(ISBLANK(T65),"",IF(T65='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T65='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T65='Past LS'!$O$25,CONCATENATE('Past LS'!$O$23,," ",'Past LS'!$O$24),"ERROR"))))))</f>
         <v/>
@@ -37409,7 +37247,7 @@
       <c r="W65" s="156"/>
       <c r="X65" s="250"/>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="66" spans="19:24" x14ac:dyDescent="0.15">
       <c r="S66" s="280" t="str">
         <f>IF(T66=1,"LS# 1",IF(T66="Xin","",IF(ISBLANK(T66),"",IF(T66='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T66='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T66='Past LS'!$O$25,CONCATENATE('Past LS'!$O$23,," ",'Past LS'!$O$24),"ERROR"))))))</f>
         <v/>
@@ -37420,7 +37258,7 @@
       <c r="W66" s="156"/>
       <c r="X66" s="250"/>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="67" spans="19:24" x14ac:dyDescent="0.15">
       <c r="S67" s="280" t="str">
         <f>IF(T67=1,"LS# 1",IF(T67="Xin","",IF(ISBLANK(T67),"",IF(T67='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T67='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T67='Past LS'!$O$25,CONCATENATE('Past LS'!$O$23,," ",'Past LS'!$O$24),"ERROR"))))))</f>
         <v/>
@@ -37431,7 +37269,7 @@
       <c r="W67" s="156"/>
       <c r="X67" s="250"/>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="68" spans="19:24" x14ac:dyDescent="0.15">
       <c r="S68" s="280" t="str">
         <f>IF(T68=1,"LS# 1",IF(T68="Xin","",IF(ISBLANK(T68),"",IF(T68='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T68='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T68='Past LS'!$O$25,CONCATENATE('Past LS'!$O$23,," ",'Past LS'!$O$24),"ERROR"))))))</f>
         <v/>
@@ -37442,7 +37280,7 @@
       <c r="W68" s="156"/>
       <c r="X68" s="250"/>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="69" spans="19:24" x14ac:dyDescent="0.15">
       <c r="S69" s="280" t="str">
         <f>IF(T69=1,"LS# 1",IF(T69="Xin","",IF(ISBLANK(T69),"",IF(T69='Past LS'!$M$25,CONCATENATE('Past LS'!$M$23,," ",'Past LS'!$M$24),IF(T69='Past LS'!$N$25,CONCATENATE('Past LS'!$N$23,," ",'Past LS'!$N$24),IF(T69='Past LS'!$O$26,CONCATENATE('Past LS'!$O$24,," ",'Past LS'!$O$25),"ERROR"))))))</f>
         <v/>
@@ -37453,18 +37291,13 @@
       <c r="W69" s="156"/>
       <c r="X69" s="250"/>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="70" spans="19:24" x14ac:dyDescent="0.15">
       <c r="S70" s="281"/>
       <c r="T70" s="146"/>
       <c r="U70" s="146"/>
       <c r="V70" s="146"/>
       <c r="W70" s="146"/>
       <c r="X70" s="149"/>
-    </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="A79" s="499"/>
-      <c r="B79" s="499"/>
-      <c r="C79" s="499"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -37498,16 +37331,16 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="60" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C1" s="60"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B4" s="282" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C4" s="283" t="e">
         <f>(MeanRatio-Intercept)/Slope</f>
@@ -37520,37 +37353,37 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="60" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B10" s="285" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C10" s="286" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D10" s="286" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E10" s="286" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F10" s="287" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B11" s="186" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C11" t="e">
         <f>-CertifiedValue/Slope</f>
@@ -37568,7 +37401,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B12" s="186" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C12" t="e">
         <f>-1/Slope</f>
@@ -37586,7 +37419,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B13" s="289" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C13" s="290" t="e">
         <f>2*C11*C12</f>
@@ -37604,7 +37437,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B14" s="294" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="C14" s="191"/>
       <c r="D14" s="191"/>
@@ -37617,15 +37450,15 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="60" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F19" s="298">
         <v>1E-3</v>
@@ -37633,41 +37466,41 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F20" s="63" t="e">
         <f>F19*CertifiedValue</f>
         <v>#NUM!</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="60" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B23" s="60" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B25" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B26" s="285" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C26" s="286" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D26" s="286" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E26" s="286" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F26" s="287" t="s">
         <v>159</v>
@@ -37678,7 +37511,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B27" s="300" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C27" s="301" t="e">
         <f>1/Slope</f>
@@ -37703,7 +37536,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B28" s="186" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -37727,7 +37560,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B29" s="186" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -37741,7 +37574,7 @@
         <v>#NUM!</v>
       </c>
       <c r="F29" s="307" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="G29" s="310" t="e">
         <f>E29/C27</f>
@@ -37750,7 +37583,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B30" s="186" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C30" s="75" t="e">
         <f>C27</f>
@@ -37772,7 +37605,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B31" s="313" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C31" s="314"/>
       <c r="D31" s="314"/>
@@ -37791,15 +37624,15 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" s="60" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B34" s="60" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B36" s="285" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C36" s="318"/>
       <c r="D36" s="318"/>
@@ -37807,7 +37640,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B37" s="300" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C37" s="320"/>
       <c r="D37" s="320"/>
@@ -37818,7 +37651,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B38" s="186" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E38" s="322" t="e">
         <f>TINV(0.05,F31)</f>
@@ -37827,7 +37660,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B39" s="294" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C39" s="191"/>
       <c r="D39" s="191"/>
@@ -37844,14 +37677,14 @@
     </row>
     <row r="42" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="B42" s="324" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C42" s="325" t="e">
         <f>CertifiedValue</f>
         <v>#NUM!</v>
       </c>
       <c r="D42" s="326" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E42" s="327" t="e">
         <f>E39</f>
@@ -37869,7 +37702,7 @@
         <v>118</v>
       </c>
       <c r="I42" s="324" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="J42" s="331" t="e">
         <f>E38</f>
@@ -37878,14 +37711,14 @@
     </row>
     <row r="43" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="B43" s="324" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C43" s="325">
         <f>RCertification!B48</f>
         <v>0</v>
       </c>
       <c r="D43" s="326" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E43" s="327">
         <f>RCertification!B50</f>
@@ -37903,7 +37736,7 @@
         <v>118</v>
       </c>
       <c r="I43" s="324" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="J43" s="331">
         <f>RCertification!B52</f>
@@ -37912,14 +37745,14 @@
     </row>
     <row r="44" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="B44" s="324" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C44" s="325">
         <f>RCertification!B54</f>
         <v>0</v>
       </c>
       <c r="D44" s="326" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E44" s="327">
         <f>RCertification!B56</f>
@@ -38195,7 +38028,7 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="AD29" s="17"/>
       <c r="AE29" s="17"/>
@@ -38310,7 +38143,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="W43" s="332" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="X43" s="333">
         <v>0.8</v>
@@ -38320,7 +38153,7 @@
     </row>
     <row r="44" spans="1:31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="334" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B44" s="335"/>
       <c r="C44" s="336"/>
@@ -38335,7 +38168,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="M45" s="495" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="N45" s="496"/>
       <c r="O45" s="496"/>
@@ -38350,33 +38183,33 @@
       <c r="A46" s="425"/>
       <c r="B46" s="426"/>
       <c r="C46" s="426" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="D46" s="427"/>
       <c r="F46" s="445" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="G46" s="446"/>
       <c r="H46" s="426"/>
       <c r="I46" s="426"/>
       <c r="J46" s="445" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="K46" s="427"/>
       <c r="M46" s="349" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="N46" s="350"/>
       <c r="O46" s="350"/>
       <c r="P46" s="351" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="Q46" s="350"/>
       <c r="R46" s="350" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="S46" s="351" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="T46" s="350" t="s">
         <v>118</v>
@@ -38389,58 +38222,58 @@
       <c r="A47" s="428"/>
       <c r="B47" s="351"/>
       <c r="C47" s="351" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D47" s="356" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="F47" s="353"/>
       <c r="G47" s="355" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H47" s="355" t="s">
         <v>62</v>
       </c>
       <c r="I47" s="355" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="J47" s="353" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K47" s="356" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="M47" s="353" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="N47" s="354" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O47" s="354" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="P47" s="355" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="Q47" s="354" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="R47" s="354" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="S47" s="355" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="T47" s="354" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="U47" s="356" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
     </row>
     <row r="48" spans="1:31" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="429" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="B48" s="430"/>
       <c r="C48" s="431" t="e">
@@ -38492,7 +38325,7 @@
     </row>
     <row r="49" spans="1:23" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="428" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B49" s="433"/>
       <c r="C49" s="415" t="e">
@@ -38541,7 +38374,7 @@
     </row>
     <row r="50" spans="1:23" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A50" s="428" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B50" s="433"/>
       <c r="C50" s="415" t="e">
@@ -38593,7 +38426,7 @@
     </row>
     <row r="51" spans="1:23" customFormat="1" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A51" s="428" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B51" s="433"/>
       <c r="C51" s="415" t="e">
@@ -38602,7 +38435,7 @@
       </c>
       <c r="D51" s="368"/>
       <c r="F51" s="399" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="G51" s="452"/>
       <c r="H51" s="452"/>
@@ -38645,7 +38478,7 @@
     </row>
     <row r="52" spans="1:23" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="428" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B52" s="433"/>
       <c r="C52" s="415" t="e">
@@ -38654,7 +38487,7 @@
       </c>
       <c r="D52" s="368"/>
       <c r="F52" s="454" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="G52" s="347"/>
       <c r="H52" s="455"/>
@@ -38688,7 +38521,7 @@
     </row>
     <row r="53" spans="1:23" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="434" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B53" s="435"/>
       <c r="C53" s="436"/>
@@ -38704,7 +38537,7 @@
         <v>86</v>
       </c>
       <c r="J53" s="460" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="K53" s="337"/>
       <c r="M53" s="386"/>
@@ -38734,12 +38567,12 @@
     </row>
     <row r="54" spans="1:23" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="428" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B54" s="438"/>
       <c r="C54" s="439">
         <f>'Std Analysis'!L5</f>
-        <v>5.1393653353487503</v>
+        <v>0</v>
       </c>
       <c r="D54" s="440" t="e">
         <f>(C54-B54)/B54</f>
@@ -38784,12 +38617,12 @@
     </row>
     <row r="55" spans="1:23" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="428" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B55" s="433"/>
       <c r="C55" s="415">
         <f>'Std Analysis'!M5</f>
-        <v>5.4762915734571597E-3</v>
+        <v>0</v>
       </c>
       <c r="D55" s="368"/>
       <c r="F55" s="349" t="s">
@@ -38831,12 +38664,12 @@
     </row>
     <row r="56" spans="1:23" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="428" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B56" s="433"/>
       <c r="C56" s="415">
         <f>C55*2</f>
-        <v>1.0952583146914319E-2</v>
+        <v>0</v>
       </c>
       <c r="D56" s="368"/>
       <c r="F56" s="349" t="s">
@@ -38875,16 +38708,16 @@
     </row>
     <row r="57" spans="1:23" customFormat="1" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A57" s="441" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B57" s="442"/>
-      <c r="C57" s="443">
+      <c r="C57" s="443" t="e">
         <f>C56/C54</f>
-        <v>2.1311158931594208E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D57" s="444"/>
       <c r="F57" s="419" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="G57" s="462"/>
       <c r="H57" s="420"/>
@@ -38949,22 +38782,22 @@
     </row>
     <row r="59" spans="1:23" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A59" s="409" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B59" s="410" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C59" s="411" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="D59" s="412" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="E59" s="412" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="F59" s="398" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="G59" s="398" t="s">
         <v>8</v>
@@ -38973,7 +38806,7 @@
         <v>2</v>
       </c>
       <c r="I59" s="348" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -39577,28 +39410,28 @@
     </row>
     <row r="72" spans="1:21" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="347" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B72" s="398" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C72" s="398" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D72" s="398" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="E72" s="347" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="F72" s="398" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="G72" s="398" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="H72" s="348" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="M72" s="386"/>
       <c r="N72" s="376"/>
@@ -39869,10 +39702,10 @@
         <v>8</v>
       </c>
       <c r="D79" s="348" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G79" s="498" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="H79" s="498"/>
       <c r="I79" s="1"/>
@@ -39909,7 +39742,7 @@
       <c r="C80" s="396"/>
       <c r="D80" s="397"/>
       <c r="G80" s="339" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H80" s="340"/>
       <c r="I80" s="1"/>
@@ -39946,7 +39779,7 @@
       <c r="C81" s="345"/>
       <c r="D81" s="481"/>
       <c r="G81" s="339" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="H81" s="340"/>
       <c r="I81" s="1"/>
@@ -39983,7 +39816,7 @@
       <c r="C82" s="345"/>
       <c r="D82" s="481"/>
       <c r="G82" s="339" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="H82" s="340"/>
       <c r="I82" s="1"/>
@@ -40020,7 +39853,7 @@
       <c r="C83" s="345"/>
       <c r="D83" s="481"/>
       <c r="G83" s="339" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="H83" s="340"/>
       <c r="I83" s="1"/>
@@ -40057,7 +39890,7 @@
       <c r="C84" s="345"/>
       <c r="D84" s="344"/>
       <c r="G84" s="339" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="H84" s="340"/>
       <c r="I84" s="1"/>
@@ -40094,7 +39927,7 @@
       <c r="C85" s="345"/>
       <c r="D85" s="344"/>
       <c r="G85" s="341" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="H85" s="342"/>
       <c r="I85" s="1"/>

--- a/src/nist_gas_srm/core/data/template.xlsx
+++ b/src/nist_gas_srm/core/data/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wpk/gits/nist-gas-srm-certificate/nist-gas-srm/src/nist_gas_srm/core/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ECE6C9-74B2-3F42-98C1-1BE1B85AC2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF043D9-F64D-8743-92B7-2AACAB5312B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2000" yWindow="660" windowWidth="27980" windowHeight="21680" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2000" yWindow="660" windowWidth="27980" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ratio Data" sheetId="1" r:id="rId1"/>
@@ -86,49 +86,6 @@
           </rPr>
           <t>Microsoft Office User:
 = variance / sum(variance)</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Krekelberg, William P. (Fed)</author>
-  </authors>
-  <commentList>
-    <comment ref="U24" authorId="0" shapeId="0" xr:uid="{3A440BC3-64DD-784A-8062-79EA0F3AFF12}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Krekelberg, William P. (Fed):</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Fit X-solution vs Y-solution</t>
         </r>
       </text>
     </comment>
@@ -1481,7 +1438,7 @@
     <numFmt numFmtId="178" formatCode="0.0000%"/>
     <numFmt numFmtId="179" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <name val="Univers"/>
@@ -1649,19 +1606,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -36166,7 +36110,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -37313,7 +37257,6 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToWidth="2" fitToHeight="3" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
